--- a/12609800.xlsx
+++ b/12609800.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A V N I S H\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8566D4D-5C6E-41CD-B3C5-24ABB36924D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FED0BA3-85FD-45C6-9103-DAA24D3100D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -260,6 +260,9 @@
   </si>
   <si>
     <t>studying for ca.</t>
+  </si>
+  <si>
+    <t>studied analytical skills</t>
   </si>
 </sst>
 </file>
@@ -2005,26 +2008,50 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B27" s="14">
+        <v>420</v>
+      </c>
+      <c r="C27" s="14">
+        <v>15</v>
+      </c>
+      <c r="D27" s="14">
+        <v>180</v>
+      </c>
+      <c r="E27" s="14">
+        <v>0</v>
+      </c>
+      <c r="F27" s="14">
+        <v>0</v>
+      </c>
+      <c r="G27" s="14">
+        <v>0</v>
+      </c>
+      <c r="H27" s="14">
+        <v>300</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>915</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>525</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>

--- a/12609800.xlsx
+++ b/12609800.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A V N I S H\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FED0BA3-85FD-45C6-9103-DAA24D3100D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45828799-8BEF-4705-AEB4-6B206E2564A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -263,6 +263,9 @@
   </si>
   <si>
     <t>studied analytical skills</t>
+  </si>
+  <si>
+    <t>studying for python ca.</t>
   </si>
 </sst>
 </file>
@@ -2054,26 +2057,50 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B28" s="14">
+        <v>420</v>
+      </c>
+      <c r="C28" s="14">
+        <v>0</v>
+      </c>
+      <c r="D28" s="14">
+        <v>120</v>
+      </c>
+      <c r="E28" s="14">
+        <v>30</v>
+      </c>
+      <c r="F28" s="14">
+        <v>150</v>
+      </c>
+      <c r="G28" s="14">
+        <v>3</v>
+      </c>
+      <c r="H28" s="14">
+        <v>240</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="13"/>

--- a/12609800.xlsx
+++ b/12609800.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A V N I S H\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45828799-8BEF-4705-AEB4-6B206E2564A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFA246FE-2C2A-4EE1-B0F2-A911D8FE3495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -266,6 +266,12 @@
   </si>
   <si>
     <t>studying for python ca.</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>studying for analytical ca.</t>
   </si>
 </sst>
 </file>
@@ -2103,26 +2109,50 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B29" s="14">
+        <v>420</v>
+      </c>
+      <c r="C29" s="14">
+        <v>0</v>
+      </c>
+      <c r="D29" s="14">
+        <v>320</v>
+      </c>
+      <c r="E29" s="14">
+        <v>0</v>
+      </c>
+      <c r="F29" s="14">
+        <v>300</v>
+      </c>
+      <c r="G29" s="14">
+        <v>6</v>
+      </c>
+      <c r="H29" s="14">
+        <v>240</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>160</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>

--- a/12609800.xlsx
+++ b/12609800.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A V N I S H\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFA246FE-2C2A-4EE1-B0F2-A911D8FE3495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4F12A24-C265-4725-BA33-2DAF4BB2A4EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -272,6 +272,9 @@
   </si>
   <si>
     <t>studying for analytical ca.</t>
+  </si>
+  <si>
+    <t>studies python.</t>
   </si>
 </sst>
 </file>
@@ -2155,26 +2158,50 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B30" s="14">
+        <v>360</v>
+      </c>
+      <c r="C30" s="14">
+        <v>0</v>
+      </c>
+      <c r="D30" s="14">
+        <v>120</v>
+      </c>
+      <c r="E30" s="14">
+        <v>30</v>
+      </c>
+      <c r="F30" s="14">
+        <v>350</v>
+      </c>
+      <c r="G30" s="14">
+        <v>7</v>
+      </c>
+      <c r="H30" s="14">
+        <v>240</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>340</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="13"/>

--- a/12609800.xlsx
+++ b/12609800.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A V N I S H\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4F12A24-C265-4725-BA33-2DAF4BB2A4EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A632660C-74B6-4C32-A91F-81973CFFA2D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -274,7 +274,10 @@
     <t>studying for analytical ca.</t>
   </si>
   <si>
-    <t>studies python.</t>
+    <t>studied python.</t>
+  </si>
+  <si>
+    <t>building logic.</t>
   </si>
 </sst>
 </file>
@@ -2204,26 +2207,50 @@
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46294</v>
+      </c>
+      <c r="B31" s="14">
+        <v>360</v>
+      </c>
+      <c r="C31" s="14">
+        <v>15</v>
+      </c>
+      <c r="D31" s="14">
+        <v>240</v>
+      </c>
+      <c r="E31" s="14">
+        <v>180</v>
+      </c>
+      <c r="F31" s="14">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14">
+        <v>120</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>915</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>525</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="13"/>

--- a/12609800.xlsx
+++ b/12609800.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A V N I S H\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A632660C-74B6-4C32-A91F-81973CFFA2D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7501FCB5-F4A1-4362-B5A8-8069330E1930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -278,6 +278,9 @@
   </si>
   <si>
     <t>building logic.</t>
+  </si>
+  <si>
+    <t>learning c++.</t>
   </si>
 </sst>
 </file>
@@ -2253,26 +2256,50 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B32" s="14">
+        <v>360</v>
+      </c>
+      <c r="C32" s="14">
+        <v>15</v>
+      </c>
+      <c r="D32" s="14">
+        <v>300</v>
+      </c>
+      <c r="E32" s="14">
+        <v>60</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>120</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>855</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>585</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="13"/>

--- a/12609800.xlsx
+++ b/12609800.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A V N I S H\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7501FCB5-F4A1-4362-B5A8-8069330E1930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE834711-C225-4191-BD13-856C64B2969F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -281,6 +281,12 @@
   </si>
   <si>
     <t>learning c++.</t>
+  </si>
+  <si>
+    <t>studying for mid terms.</t>
+  </si>
+  <si>
+    <t>nothing much to write .</t>
   </si>
 </sst>
 </file>
@@ -2302,224 +2308,464 @@
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B33" s="14">
+        <v>240</v>
+      </c>
+      <c r="C33" s="14">
+        <v>20</v>
+      </c>
+      <c r="D33" s="14">
+        <v>180</v>
+      </c>
+      <c r="E33" s="14">
+        <v>180</v>
+      </c>
+      <c r="F33" s="14">
+        <v>0</v>
+      </c>
+      <c r="G33" s="14">
+        <v>0</v>
+      </c>
+      <c r="H33" s="14">
+        <v>120</v>
+      </c>
+      <c r="I33" s="15">
+        <f>IF(SUM(B33:F33,H33)=0,"",SUM(B33:F33,H33))</f>
+        <v>740</v>
+      </c>
+      <c r="J33" s="15">
+        <f>IF(I33="","",1440-I33)</f>
+        <v>700</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A34" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B34" s="14">
+        <v>300</v>
+      </c>
+      <c r="C34" s="14">
+        <v>15</v>
+      </c>
+      <c r="D34" s="14">
+        <v>240</v>
+      </c>
+      <c r="E34" s="14">
+        <v>60</v>
+      </c>
+      <c r="F34" s="14">
+        <v>0</v>
+      </c>
+      <c r="G34" s="14">
+        <v>0</v>
+      </c>
+      <c r="H34" s="14">
+        <v>60</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>675</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+        <v>765</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A35" s="13">
+        <v>46299</v>
+      </c>
+      <c r="B35" s="14">
+        <v>360</v>
+      </c>
+      <c r="C35" s="14">
+        <v>15</v>
+      </c>
+      <c r="D35" s="14">
+        <v>300</v>
+      </c>
+      <c r="E35" s="14">
+        <v>150</v>
+      </c>
+      <c r="F35" s="14">
+        <v>0</v>
+      </c>
+      <c r="G35" s="14">
+        <v>0</v>
+      </c>
+      <c r="H35" s="14">
+        <v>180</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>1005</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+        <v>435</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A36" s="13">
+        <v>46300</v>
+      </c>
+      <c r="B36" s="14">
+        <v>420</v>
+      </c>
+      <c r="C36" s="14">
+        <v>0</v>
+      </c>
+      <c r="D36" s="14">
+        <v>300</v>
+      </c>
+      <c r="E36" s="14">
+        <v>300</v>
+      </c>
+      <c r="F36" s="14">
+        <v>150</v>
+      </c>
+      <c r="G36" s="14">
+        <v>3</v>
+      </c>
+      <c r="H36" s="14">
+        <v>180</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1350</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+        <v>90</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A37" s="13">
+        <v>46301</v>
+      </c>
+      <c r="B37" s="14">
+        <v>420</v>
+      </c>
+      <c r="C37" s="14">
+        <v>0</v>
+      </c>
+      <c r="D37" s="14">
+        <v>240</v>
+      </c>
+      <c r="E37" s="14">
+        <v>60</v>
+      </c>
+      <c r="F37" s="14">
+        <v>350</v>
+      </c>
+      <c r="G37" s="14">
+        <v>7</v>
+      </c>
+      <c r="H37" s="14">
+        <v>240</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1310</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+        <v>130</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A38" s="13">
+        <v>46302</v>
+      </c>
+      <c r="B38" s="14">
+        <v>360</v>
+      </c>
+      <c r="C38" s="14">
+        <v>0</v>
+      </c>
+      <c r="D38" s="14">
+        <v>180</v>
+      </c>
+      <c r="E38" s="14">
+        <v>0</v>
+      </c>
+      <c r="F38" s="14">
+        <v>150</v>
+      </c>
+      <c r="G38" s="14">
+        <v>3</v>
+      </c>
+      <c r="H38" s="14">
+        <v>180</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+        <v>570</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A39" s="13">
+        <v>46303</v>
+      </c>
+      <c r="B39" s="14">
+        <v>420</v>
+      </c>
+      <c r="C39" s="14">
+        <v>15</v>
+      </c>
+      <c r="D39" s="14">
+        <v>180</v>
+      </c>
+      <c r="E39" s="14">
+        <v>120</v>
+      </c>
+      <c r="F39" s="14">
+        <v>0</v>
+      </c>
+      <c r="G39" s="14">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14">
+        <v>120</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>855</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+        <v>585</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A40" s="13">
+        <v>46304</v>
+      </c>
+      <c r="B40" s="14">
+        <v>480</v>
+      </c>
+      <c r="C40" s="14">
+        <v>15</v>
+      </c>
+      <c r="D40" s="14">
+        <v>240</v>
+      </c>
+      <c r="E40" s="14">
+        <v>120</v>
+      </c>
+      <c r="F40" s="14">
+        <v>0</v>
+      </c>
+      <c r="G40" s="14">
+        <v>0</v>
+      </c>
+      <c r="H40" s="14">
+        <v>180</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>1035</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+        <v>405</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A41" s="13">
+        <v>46305</v>
+      </c>
+      <c r="B41" s="14">
+        <v>300</v>
+      </c>
+      <c r="C41" s="14">
+        <v>0</v>
+      </c>
+      <c r="D41" s="14">
+        <v>480</v>
+      </c>
+      <c r="E41" s="14">
+        <v>0</v>
+      </c>
+      <c r="F41" s="14">
+        <v>0</v>
+      </c>
+      <c r="G41" s="14">
+        <v>0</v>
+      </c>
+      <c r="H41" s="14">
+        <v>180</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+        <v>480</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A42" s="13">
+        <v>46306</v>
+      </c>
+      <c r="B42" s="14">
+        <v>360</v>
+      </c>
+      <c r="C42" s="14">
+        <v>15</v>
+      </c>
+      <c r="D42" s="14">
+        <v>480</v>
+      </c>
+      <c r="E42" s="14">
+        <v>0</v>
+      </c>
+      <c r="F42" s="14">
+        <v>0</v>
+      </c>
+      <c r="G42" s="14">
+        <v>0</v>
+      </c>
+      <c r="H42" s="14">
+        <v>180</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>1035</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+        <v>405</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="13"/>
